--- a/ig/nr-add-sato2-profile/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/ig/nr-add-sato2-profile/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4835" uniqueCount="704">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4835" uniqueCount="705">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-17T15:33:27+00:00</t>
+    <t>2023-11-17T15:40:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -441,6 +441,9 @@
   </si>
   <si>
     <t>Uri identifiant les systèmes tiers ayant envoyé la ressource. L’uri est sous la forme d’un oid : « urn:oid:xx.xx.xx »</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -3568,10 +3571,10 @@
         <v>136</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3621,7 +3624,7 @@
         <v>80</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -3656,10 +3659,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -3682,16 +3685,16 @@
         <v>92</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -3741,7 +3744,7 @@
         <v>80</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -3776,10 +3779,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3802,16 +3805,16 @@
         <v>92</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3837,13 +3840,13 @@
         <v>80</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>80</v>
@@ -3861,7 +3864,7 @@
         <v>80</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -3882,10 +3885,10 @@
         <v>80</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>80</v>
@@ -3896,10 +3899,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3922,16 +3925,16 @@
         <v>92</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3957,13 +3960,13 @@
         <v>80</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>80</v>
@@ -3981,7 +3984,7 @@
         <v>80</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -4002,10 +4005,10 @@
         <v>80</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>80</v>
@@ -4016,10 +4019,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -4045,13 +4048,13 @@
         <v>135</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -4101,7 +4104,7 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -4136,10 +4139,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4162,16 +4165,16 @@
         <v>80</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4197,13 +4200,13 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>80</v>
@@ -4221,7 +4224,7 @@
         <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -4256,14 +4259,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -4282,16 +4285,16 @@
         <v>80</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4341,7 +4344,7 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -4365,7 +4368,7 @@
         <v>80</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>80</v>
@@ -4376,14 +4379,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4402,16 +4405,16 @@
         <v>80</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4461,7 +4464,7 @@
         <v>80</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -4496,10 +4499,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4528,7 +4531,7 @@
         <v>115</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N17" t="s" s="2">
         <v>117</v>
@@ -4581,7 +4584,7 @@
         <v>120</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -4616,13 +4619,13 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>80</v>
@@ -4644,13 +4647,13 @@
         <v>80</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4701,7 +4704,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -4736,13 +4739,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>80</v>
@@ -4764,13 +4767,13 @@
         <v>80</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4821,7 +4824,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4856,13 +4859,13 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>113</v>
@@ -4884,13 +4887,13 @@
         <v>80</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>117</v>
@@ -4943,7 +4946,7 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4978,13 +4981,13 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>80</v>
@@ -5006,13 +5009,13 @@
         <v>80</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -5063,7 +5066,7 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -5098,10 +5101,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5127,16 +5130,16 @@
         <v>114</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>117</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>80</v>
@@ -5185,7 +5188,7 @@
         <v>120</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -5220,10 +5223,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5246,17 +5249,17 @@
         <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>80</v>
@@ -5305,7 +5308,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -5320,19 +5323,19 @@
         <v>104</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>80</v>
@@ -5340,14 +5343,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -5366,19 +5369,19 @@
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>80</v>
@@ -5427,7 +5430,7 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -5439,19 +5442,19 @@
         <v>103</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>80</v>
@@ -5462,14 +5465,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5488,16 +5491,16 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5547,7 +5550,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -5559,19 +5562,19 @@
         <v>103</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>80</v>
@@ -5582,10 +5585,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5608,19 +5611,19 @@
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>80</v>
@@ -5645,13 +5648,13 @@
         <v>80</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>80</v>
@@ -5669,7 +5672,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>91</v>
@@ -5684,19 +5687,19 @@
         <v>104</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>80</v>
@@ -5704,10 +5707,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5730,19 +5733,19 @@
         <v>80</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>80</v>
@@ -5767,19 +5770,19 @@
         <v>80</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AC27" s="2"/>
       <c r="AD27" t="s" s="2">
@@ -5789,7 +5792,7 @@
         <v>120</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5810,13 +5813,13 @@
         <v>80</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>80</v>
@@ -5824,13 +5827,13 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>80</v>
@@ -5852,19 +5855,19 @@
         <v>80</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>80</v>
@@ -5889,13 +5892,13 @@
         <v>80</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>80</v>
@@ -5913,7 +5916,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5934,13 +5937,13 @@
         <v>80</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>80</v>
@@ -5948,10 +5951,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6066,10 +6069,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6186,10 +6189,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6212,19 +6215,19 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>80</v>
@@ -6273,7 +6276,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -6294,10 +6297,10 @@
         <v>80</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>80</v>
@@ -6308,10 +6311,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6426,10 +6429,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6546,10 +6549,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6575,23 +6578,23 @@
         <v>135</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>80</v>
@@ -6633,7 +6636,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6654,10 +6657,10 @@
         <v>80</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>80</v>
@@ -6668,10 +6671,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6697,13 +6700,13 @@
         <v>107</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6753,7 +6756,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6774,10 +6777,10 @@
         <v>80</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>80</v>
@@ -6788,10 +6791,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6814,26 +6817,26 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>80</v>
@@ -6875,7 +6878,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6896,10 +6899,10 @@
         <v>80</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>80</v>
@@ -6910,10 +6913,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6939,16 +6942,16 @@
         <v>107</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>80</v>
@@ -6997,7 +7000,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -7018,10 +7021,10 @@
         <v>80</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>80</v>
@@ -7032,10 +7035,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7058,19 +7061,19 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>80</v>
@@ -7119,7 +7122,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -7140,10 +7143,10 @@
         <v>80</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>80</v>
@@ -7154,10 +7157,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7183,16 +7186,16 @@
         <v>107</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>80</v>
@@ -7241,7 +7244,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -7262,10 +7265,10 @@
         <v>80</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>80</v>
@@ -7276,14 +7279,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7302,19 +7305,19 @@
         <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>80</v>
@@ -7339,13 +7342,13 @@
         <v>80</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>80</v>
@@ -7363,7 +7366,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>91</v>
@@ -7378,30 +7381,30 @@
         <v>104</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7516,10 +7519,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7636,10 +7639,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7662,19 +7665,19 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>80</v>
@@ -7711,7 +7714,7 @@
         <v>80</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
@@ -7721,7 +7724,7 @@
         <v>120</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7742,10 +7745,10 @@
         <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>80</v>
@@ -7756,13 +7759,13 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>80</v>
@@ -7784,19 +7787,19 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>80</v>
@@ -7845,7 +7848,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7866,10 +7869,10 @@
         <v>80</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>80</v>
@@ -7880,10 +7883,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7998,10 +8001,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8118,10 +8121,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8147,23 +8150,23 @@
         <v>135</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>80</v>
@@ -8205,7 +8208,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -8226,10 +8229,10 @@
         <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>80</v>
@@ -8240,10 +8243,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8269,13 +8272,13 @@
         <v>107</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8325,7 +8328,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -8346,10 +8349,10 @@
         <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>80</v>
@@ -8360,10 +8363,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8386,26 +8389,26 @@
         <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>80</v>
@@ -8447,7 +8450,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -8468,10 +8471,10 @@
         <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>80</v>
@@ -8482,10 +8485,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8511,16 +8514,16 @@
         <v>107</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -8569,7 +8572,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -8590,10 +8593,10 @@
         <v>80</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>80</v>
@@ -8604,10 +8607,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8630,19 +8633,19 @@
         <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
@@ -8691,7 +8694,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8712,10 +8715,10 @@
         <v>80</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>80</v>
@@ -8726,10 +8729,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8755,16 +8758,16 @@
         <v>107</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -8813,7 +8816,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8834,10 +8837,10 @@
         <v>80</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>80</v>
@@ -8848,10 +8851,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8874,19 +8877,19 @@
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>80</v>
@@ -8935,7 +8938,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8947,22 +8950,22 @@
         <v>103</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>80</v>
@@ -8970,10 +8973,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8996,16 +8999,16 @@
         <v>92</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -9055,7 +9058,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -9067,7 +9070,7 @@
         <v>103</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>80</v>
@@ -9076,13 +9079,13 @@
         <v>80</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>80</v>
@@ -9090,14 +9093,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -9116,19 +9119,19 @@
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>80</v>
@@ -9177,7 +9180,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -9189,22 +9192,22 @@
         <v>103</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>80</v>
@@ -9212,14 +9215,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -9238,19 +9241,19 @@
         <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>80</v>
@@ -9299,7 +9302,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -9308,25 +9311,25 @@
         <v>91</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>80</v>
@@ -9334,10 +9337,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9363,13 +9366,13 @@
         <v>129</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9419,7 +9422,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -9440,13 +9443,13 @@
         <v>80</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>80</v>
@@ -9454,10 +9457,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9480,19 +9483,19 @@
         <v>92</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>80</v>
@@ -9541,7 +9544,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -9553,22 +9556,22 @@
         <v>103</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>80</v>
@@ -9576,10 +9579,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9602,19 +9605,19 @@
         <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>80</v>
@@ -9651,17 +9654,17 @@
         <v>80</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AC59" s="2"/>
       <c r="AD59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9670,7 +9673,7 @@
         <v>91</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>104</v>
@@ -9679,30 +9682,30 @@
         <v>80</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>80</v>
@@ -9724,19 +9727,19 @@
         <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>80</v>
@@ -9785,7 +9788,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9794,7 +9797,7 @@
         <v>91</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>104</v>
@@ -9803,27 +9806,27 @@
         <v>80</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9938,10 +9941,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10058,10 +10061,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10084,19 +10087,19 @@
         <v>92</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>80</v>
@@ -10145,7 +10148,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -10166,10 +10169,10 @@
         <v>80</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>80</v>
@@ -10180,10 +10183,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10206,25 +10209,25 @@
         <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q64" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="R64" t="s" s="2">
         <v>80</v>
@@ -10245,13 +10248,13 @@
         <v>80</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>80</v>
@@ -10269,7 +10272,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -10290,10 +10293,10 @@
         <v>80</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>80</v>
@@ -10304,10 +10307,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10333,16 +10336,16 @@
         <v>107</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>80</v>
@@ -10391,7 +10394,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -10412,10 +10415,10 @@
         <v>80</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>80</v>
@@ -10426,10 +10429,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10455,23 +10458,23 @@
         <v>135</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q66" s="2"/>
       <c r="R66" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="S66" t="s" s="2">
         <v>80</v>
@@ -10513,7 +10516,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -10522,7 +10525,7 @@
         <v>91</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>104</v>
@@ -10534,10 +10537,10 @@
         <v>80</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>80</v>
@@ -10548,10 +10551,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10574,26 +10577,26 @@
         <v>92</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="S67" t="s" s="2">
         <v>80</v>
@@ -10635,7 +10638,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10656,10 +10659,10 @@
         <v>80</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>80</v>
@@ -10670,10 +10673,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10696,19 +10699,19 @@
         <v>80</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>80</v>
@@ -10733,13 +10736,13 @@
         <v>80</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>80</v>
@@ -10757,7 +10760,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10766,7 +10769,7 @@
         <v>91</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>104</v>
@@ -10781,7 +10784,7 @@
         <v>105</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>80</v>
@@ -10792,10 +10795,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10910,10 +10913,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11030,10 +11033,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11056,19 +11059,19 @@
         <v>92</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>80</v>
@@ -11117,7 +11120,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -11138,10 +11141,10 @@
         <v>80</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>80</v>
@@ -11152,10 +11155,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11270,10 +11273,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11390,10 +11393,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11419,16 +11422,16 @@
         <v>135</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>80</v>
@@ -11477,7 +11480,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -11498,10 +11501,10 @@
         <v>80</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>80</v>
@@ -11512,10 +11515,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11541,13 +11544,13 @@
         <v>107</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11597,7 +11600,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -11618,10 +11621,10 @@
         <v>80</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>80</v>
@@ -11632,10 +11635,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11658,19 +11661,19 @@
         <v>92</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>80</v>
@@ -11719,7 +11722,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -11740,10 +11743,10 @@
         <v>80</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>80</v>
@@ -11754,10 +11757,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11783,16 +11786,16 @@
         <v>107</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>80</v>
@@ -11841,7 +11844,7 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11862,10 +11865,10 @@
         <v>80</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>80</v>
@@ -11876,10 +11879,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11902,19 +11905,19 @@
         <v>92</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>80</v>
@@ -11963,7 +11966,7 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11984,10 +11987,10 @@
         <v>80</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>80</v>
@@ -11998,10 +12001,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12027,16 +12030,16 @@
         <v>107</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>80</v>
@@ -12085,7 +12088,7 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -12106,10 +12109,10 @@
         <v>80</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>80</v>
@@ -12120,14 +12123,14 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -12146,19 +12149,19 @@
         <v>80</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>80</v>
@@ -12183,11 +12186,11 @@
         <v>80</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>80</v>
@@ -12205,7 +12208,7 @@
         <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -12223,27 +12226,27 @@
         <v>80</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12266,19 +12269,19 @@
         <v>80</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>80</v>
@@ -12327,7 +12330,7 @@
         <v>80</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -12348,10 +12351,10 @@
         <v>80</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>80</v>
@@ -12362,10 +12365,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12388,16 +12391,16 @@
         <v>80</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12423,13 +12426,13 @@
         <v>80</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>80</v>
@@ -12447,7 +12450,7 @@
         <v>80</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -12465,27 +12468,27 @@
         <v>80</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12600,10 +12603,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12720,10 +12723,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12746,19 +12749,19 @@
         <v>92</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>80</v>
@@ -12783,11 +12786,11 @@
         <v>80</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Y85" s="2"/>
       <c r="Z85" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>80</v>
@@ -12805,7 +12808,7 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12826,10 +12829,10 @@
         <v>80</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>80</v>
@@ -12840,10 +12843,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12869,16 +12872,16 @@
         <v>107</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>80</v>
@@ -12927,7 +12930,7 @@
         <v>80</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12948,10 +12951,10 @@
         <v>80</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>80</v>
@@ -12962,10 +12965,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12988,19 +12991,19 @@
         <v>80</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>80</v>
@@ -13025,13 +13028,13 @@
         <v>80</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>80</v>
@@ -13049,7 +13052,7 @@
         <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -13070,10 +13073,10 @@
         <v>80</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>80</v>
@@ -13084,10 +13087,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13202,10 +13205,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13322,10 +13325,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13348,19 +13351,19 @@
         <v>92</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>80</v>
@@ -13385,11 +13388,11 @@
         <v>80</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Y90" s="2"/>
       <c r="Z90" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>80</v>
@@ -13407,7 +13410,7 @@
         <v>80</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -13428,10 +13431,10 @@
         <v>80</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>80</v>
@@ -13442,10 +13445,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13471,16 +13474,16 @@
         <v>107</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>80</v>
@@ -13529,7 +13532,7 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -13550,10 +13553,10 @@
         <v>80</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>80</v>
@@ -13564,10 +13567,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13590,16 +13593,16 @@
         <v>80</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13649,7 +13652,7 @@
         <v>80</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13661,33 +13664,33 @@
         <v>103</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13710,16 +13713,16 @@
         <v>80</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13769,7 +13772,7 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13781,33 +13784,33 @@
         <v>103</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13830,19 +13833,19 @@
         <v>80</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>80</v>
@@ -13891,7 +13894,7 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13903,7 +13906,7 @@
         <v>103</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>80</v>
@@ -13912,10 +13915,10 @@
         <v>80</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>80</v>
@@ -13926,10 +13929,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14044,10 +14047,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14164,14 +14167,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -14193,16 +14196,16 @@
         <v>114</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>117</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>80</v>
@@ -14251,7 +14254,7 @@
         <v>80</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -14286,10 +14289,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14312,16 +14315,16 @@
         <v>80</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -14371,7 +14374,7 @@
         <v>80</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -14380,10 +14383,10 @@
         <v>91</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>80</v>
@@ -14392,10 +14395,10 @@
         <v>80</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>80</v>
@@ -14406,10 +14409,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14432,16 +14435,16 @@
         <v>80</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -14491,7 +14494,7 @@
         <v>80</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -14500,10 +14503,10 @@
         <v>91</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>80</v>
@@ -14512,10 +14515,10 @@
         <v>80</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>80</v>
@@ -14526,10 +14529,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14552,19 +14555,19 @@
         <v>80</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>80</v>
@@ -14589,13 +14592,13 @@
         <v>80</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>80</v>
@@ -14613,7 +14616,7 @@
         <v>80</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -14631,13 +14634,13 @@
         <v>80</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>80</v>
@@ -14648,10 +14651,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14674,19 +14677,19 @@
         <v>80</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>80</v>
@@ -14711,13 +14714,13 @@
         <v>80</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>80</v>
@@ -14735,7 +14738,7 @@
         <v>80</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -14753,13 +14756,13 @@
         <v>80</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>80</v>
@@ -14770,10 +14773,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14888,10 +14891,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15008,10 +15011,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15034,19 +15037,19 @@
         <v>92</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>80</v>
@@ -15095,7 +15098,7 @@
         <v>80</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -15116,10 +15119,10 @@
         <v>80</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>80</v>
@@ -15130,10 +15133,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15248,10 +15251,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15368,10 +15371,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15397,16 +15400,16 @@
         <v>135</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>80</v>
@@ -15455,7 +15458,7 @@
         <v>80</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -15476,10 +15479,10 @@
         <v>80</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>80</v>
@@ -15490,10 +15493,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15519,13 +15522,13 @@
         <v>107</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -15575,7 +15578,7 @@
         <v>80</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>78</v>
@@ -15596,10 +15599,10 @@
         <v>80</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>80</v>
@@ -15610,10 +15613,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15636,19 +15639,19 @@
         <v>92</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>80</v>
@@ -15697,7 +15700,7 @@
         <v>80</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -15718,10 +15721,10 @@
         <v>80</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>80</v>
@@ -15732,10 +15735,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15761,16 +15764,16 @@
         <v>107</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>80</v>
@@ -15819,7 +15822,7 @@
         <v>80</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -15840,10 +15843,10 @@
         <v>80</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>80</v>
@@ -15854,10 +15857,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15880,19 +15883,19 @@
         <v>92</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>80</v>
@@ -15941,7 +15944,7 @@
         <v>80</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -15962,10 +15965,10 @@
         <v>80</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>80</v>
@@ -15976,10 +15979,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16005,16 +16008,16 @@
         <v>107</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>80</v>
@@ -16063,7 +16066,7 @@
         <v>80</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -16084,10 +16087,10 @@
         <v>80</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>80</v>
@@ -16098,10 +16101,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16124,19 +16127,19 @@
         <v>80</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>80</v>
@@ -16185,7 +16188,7 @@
         <v>80</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -16197,7 +16200,7 @@
         <v>103</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>80</v>
@@ -16206,10 +16209,10 @@
         <v>80</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>80</v>
@@ -16220,10 +16223,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16249,13 +16252,13 @@
         <v>107</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -16305,7 +16308,7 @@
         <v>80</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>78</v>
@@ -16326,10 +16329,10 @@
         <v>80</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>80</v>
@@ -16340,10 +16343,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16366,16 +16369,16 @@
         <v>92</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -16425,7 +16428,7 @@
         <v>80</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
@@ -16437,7 +16440,7 @@
         <v>103</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>80</v>
@@ -16446,10 +16449,10 @@
         <v>80</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>80</v>
@@ -16460,10 +16463,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16486,16 +16489,16 @@
         <v>92</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -16545,7 +16548,7 @@
         <v>80</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
@@ -16557,7 +16560,7 @@
         <v>103</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>80</v>
@@ -16566,10 +16569,10 @@
         <v>80</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>80</v>
@@ -16580,10 +16583,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16606,19 +16609,19 @@
         <v>92</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>80</v>
@@ -16667,7 +16670,7 @@
         <v>80</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>78</v>
@@ -16679,7 +16682,7 @@
         <v>103</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>80</v>
@@ -16688,10 +16691,10 @@
         <v>80</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>80</v>
@@ -16702,10 +16705,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16820,10 +16823,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16940,14 +16943,14 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
@@ -16969,16 +16972,16 @@
         <v>114</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="N120" t="s" s="2">
         <v>117</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>80</v>
@@ -17027,7 +17030,7 @@
         <v>80</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>78</v>
@@ -17062,10 +17065,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17088,19 +17091,19 @@
         <v>92</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>80</v>
@@ -17125,13 +17128,13 @@
         <v>80</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>80</v>
@@ -17149,7 +17152,7 @@
         <v>80</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>91</v>
@@ -17167,16 +17170,16 @@
         <v>80</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AO121" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AP121" t="s" s="2">
         <v>80</v>
@@ -17184,10 +17187,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17210,19 +17213,19 @@
         <v>92</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>80</v>
@@ -17247,13 +17250,13 @@
         <v>80</v>
       </c>
       <c r="X122" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Y122" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="Z122" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>80</v>
@@ -17271,7 +17274,7 @@
         <v>80</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -17280,7 +17283,7 @@
         <v>91</v>
       </c>
       <c r="AI122" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AJ122" t="s" s="2">
         <v>104</v>
@@ -17289,27 +17292,27 @@
         <v>80</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP122" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17332,19 +17335,19 @@
         <v>80</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>80</v>
@@ -17369,13 +17372,13 @@
         <v>80</v>
       </c>
       <c r="X123" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y123" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="Z123" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>80</v>
@@ -17393,7 +17396,7 @@
         <v>80</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
@@ -17402,7 +17405,7 @@
         <v>91</v>
       </c>
       <c r="AI123" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AJ123" t="s" s="2">
         <v>104</v>
@@ -17417,7 +17420,7 @@
         <v>105</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>80</v>
@@ -17428,14 +17431,14 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
@@ -17454,19 +17457,19 @@
         <v>80</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>80</v>
@@ -17491,31 +17494,31 @@
         <v>80</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y124" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="Z124" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AA124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF124" t="s" s="2">
         <v>700</v>
-      </c>
-      <c r="Z124" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="AA124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF124" t="s" s="2">
-        <v>699</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
@@ -17533,27 +17536,27 @@
         <v>80</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP124" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17579,16 +17582,16 @@
         <v>81</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>80</v>
@@ -17637,7 +17640,7 @@
         <v>80</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -17658,10 +17661,10 @@
         <v>80</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>80</v>

--- a/ig/nr-add-sato2-profile/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/ig/nr-add-sato2-profile/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-17T15:40:40+00:00</t>
+    <t>2023-11-23T10:07:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
